--- a/Module_4_Applied_Biostatistics/Data/Coloc_Example.xlsx
+++ b/Module_4_Applied_Biostatistics/Data/Coloc_Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sven\Desktop\Bioinformatik\ABI-2026-2\Module_4_Applied_Biostatistics\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36E02FED-B768-458A-BBC6-E92A81E86BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F29009-A970-41E8-8B3E-366ADADA9AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{0D67E6D3-F4DA-442B-B9DB-6DE0AB488676}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0D67E6D3-F4DA-442B-B9DB-6DE0AB488676}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="7">
   <si>
     <t>Strain</t>
-  </si>
-  <si>
-    <t>Rep</t>
   </si>
   <si>
     <t>Cell</t>
@@ -58,15 +55,27 @@
   <si>
     <t>Mut</t>
   </si>
+  <si>
+    <t>Replicate</t>
+  </si>
+  <si>
+    <t>Mut2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -96,7 +105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -112,7 +121,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -428,26 +437,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A8A19A-3DED-438C-97C1-A45C22CF7CE5}">
-  <dimension ref="A1:D113"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D147"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -464,13 +473,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -478,13 +487,13 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -492,13 +501,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -506,13 +515,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -520,60 +529,60 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>0.14000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>0.31</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -587,7 +596,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -601,7 +610,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -615,7 +624,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -629,7 +638,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -643,7 +652,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -657,7 +666,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -671,7 +680,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -685,7 +694,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -699,7 +708,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -713,7 +722,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -727,7 +736,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -741,7 +750,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -755,7 +764,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -769,7 +778,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -783,7 +792,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -797,7 +806,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -811,7 +820,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -825,7 +834,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -839,7 +848,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -853,7 +862,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -867,7 +876,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -881,7 +890,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -895,7 +904,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -909,7 +918,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -923,7 +932,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -937,7 +946,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37">
         <v>3</v>
@@ -951,7 +960,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -965,7 +974,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -979,7 +988,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -993,7 +1002,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41">
         <v>3</v>
@@ -1007,7 +1016,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42">
         <v>3</v>
@@ -1021,7 +1030,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B43">
         <v>3</v>
@@ -1035,7 +1044,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -1049,7 +1058,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -1063,7 +1072,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -1077,7 +1086,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47">
         <v>3</v>
@@ -1091,7 +1100,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B48">
         <v>3</v>
@@ -1105,7 +1114,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B49">
         <v>3</v>
@@ -1119,7 +1128,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50">
         <v>3</v>
@@ -1133,7 +1142,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B51">
         <v>3</v>
@@ -1147,7 +1156,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52">
         <v>3</v>
@@ -1161,7 +1170,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53">
         <v>3</v>
@@ -1175,7 +1184,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>3</v>
@@ -1189,7 +1198,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55">
         <v>3</v>
@@ -1203,7 +1212,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56">
         <v>3</v>
@@ -1217,7 +1226,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B57">
         <v>3</v>
@@ -1231,7 +1240,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -1245,7 +1254,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B59">
         <v>3</v>
@@ -1259,7 +1268,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B60">
         <v>3</v>
@@ -1273,7 +1282,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B61">
         <v>3</v>
@@ -1287,7 +1296,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B62">
         <v>3</v>
@@ -1301,7 +1310,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -1315,7 +1324,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -1329,7 +1338,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B65">
         <v>3</v>
@@ -1343,7 +1352,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -1357,7 +1366,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -1371,7 +1380,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -1385,7 +1394,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -1399,7 +1408,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -1413,7 +1422,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -1427,7 +1436,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -1441,7 +1450,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -1455,7 +1464,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -1469,7 +1478,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -1483,7 +1492,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -1497,7 +1506,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -1511,7 +1520,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -1525,7 +1534,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -1539,7 +1548,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -1553,7 +1562,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -1567,7 +1576,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -1581,7 +1590,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -1595,7 +1604,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -1609,7 +1618,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -1623,7 +1632,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -1637,7 +1646,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -1651,7 +1660,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -1665,7 +1674,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -1679,7 +1688,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -1693,7 +1702,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -1707,7 +1716,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -1721,7 +1730,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -1735,7 +1744,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -1749,7 +1758,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -1763,7 +1772,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -1777,7 +1786,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -1791,7 +1800,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -1805,7 +1814,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -1819,7 +1828,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -1833,7 +1842,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -1847,7 +1856,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B102">
         <v>2</v>
@@ -1861,7 +1870,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B103">
         <v>3</v>
@@ -1875,7 +1884,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B104">
         <v>3</v>
@@ -1889,7 +1898,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B105">
         <v>3</v>
@@ -1903,7 +1912,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B106">
         <v>3</v>
@@ -1917,7 +1926,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B107">
         <v>3</v>
@@ -1931,7 +1940,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B108">
         <v>3</v>
@@ -1945,7 +1954,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -1959,7 +1968,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B110">
         <v>3</v>
@@ -1973,7 +1982,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B111">
         <v>3</v>
@@ -1987,7 +1996,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B112">
         <v>3</v>
@@ -2001,7 +2010,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B113">
         <v>3</v>
@@ -2013,7 +2022,484 @@
         <v>0.08</v>
       </c>
     </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>6</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>6</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>3</v>
+      </c>
+      <c r="D116">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>4</v>
+      </c>
+      <c r="D117">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>5</v>
+      </c>
+      <c r="D118">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>6</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>6</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>6</v>
+      </c>
+      <c r="B122">
+        <v>2</v>
+      </c>
+      <c r="C122">
+        <v>3</v>
+      </c>
+      <c r="D122">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123">
+        <v>4</v>
+      </c>
+      <c r="D123">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>6</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124">
+        <v>5</v>
+      </c>
+      <c r="D124">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>6</v>
+      </c>
+      <c r="B125">
+        <v>2</v>
+      </c>
+      <c r="C125">
+        <v>6</v>
+      </c>
+      <c r="D125">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>6</v>
+      </c>
+      <c r="B126">
+        <v>2</v>
+      </c>
+      <c r="C126">
+        <v>7</v>
+      </c>
+      <c r="D126">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>6</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127">
+        <v>8</v>
+      </c>
+      <c r="D127">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>6</v>
+      </c>
+      <c r="B129">
+        <v>3</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>6</v>
+      </c>
+      <c r="B130">
+        <v>3</v>
+      </c>
+      <c r="C130">
+        <v>3</v>
+      </c>
+      <c r="D130">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>6</v>
+      </c>
+      <c r="B131">
+        <v>3</v>
+      </c>
+      <c r="C131">
+        <v>4</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>6</v>
+      </c>
+      <c r="B132">
+        <v>3</v>
+      </c>
+      <c r="C132">
+        <v>5</v>
+      </c>
+      <c r="D132">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>6</v>
+      </c>
+      <c r="B133">
+        <v>3</v>
+      </c>
+      <c r="C133">
+        <v>6</v>
+      </c>
+      <c r="D133">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>6</v>
+      </c>
+      <c r="B134">
+        <v>3</v>
+      </c>
+      <c r="C134">
+        <v>7</v>
+      </c>
+      <c r="D134">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>6</v>
+      </c>
+      <c r="B135">
+        <v>3</v>
+      </c>
+      <c r="C135">
+        <v>8</v>
+      </c>
+      <c r="D135">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>6</v>
+      </c>
+      <c r="B136">
+        <v>3</v>
+      </c>
+      <c r="C136">
+        <v>9</v>
+      </c>
+      <c r="D136">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137">
+        <v>4</v>
+      </c>
+      <c r="C137">
+        <v>10</v>
+      </c>
+      <c r="D137">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>6</v>
+      </c>
+      <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="C138">
+        <v>11</v>
+      </c>
+      <c r="D138">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>6</v>
+      </c>
+      <c r="B139">
+        <v>4</v>
+      </c>
+      <c r="C139">
+        <v>12</v>
+      </c>
+      <c r="D139">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>3</v>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+      <c r="D140">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>3</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141">
+        <v>3</v>
+      </c>
+      <c r="D141">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>3</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142">
+        <v>4</v>
+      </c>
+      <c r="D142">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>3</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143">
+        <v>5</v>
+      </c>
+      <c r="D143">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>3</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144">
+        <v>6</v>
+      </c>
+      <c r="D144">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>3</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="C145">
+        <v>7</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>3</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146">
+        <v>8</v>
+      </c>
+      <c r="D146">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>3</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147">
+        <v>9</v>
+      </c>
+      <c r="D147">
+        <v>0.24</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>